--- a/lab2/график_OpenMP.xlsx
+++ b/lab2/график_OpenMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\source\repos\parallel programming\lab2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{875A7ED3-B4E2-4B38-9761-D8643741552B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310BB9E3-9397-4399-A97E-945CD04F760C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>Размер, (эл х эл)</t>
   </si>
@@ -45,6 +45,12 @@
   </si>
   <si>
     <t>Время OpenMP, мс</t>
+  </si>
+  <si>
+    <t>Время MPI, мс</t>
+  </si>
+  <si>
+    <t>Время CUDA, мс</t>
   </si>
 </sst>
 </file>
@@ -68,7 +74,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -91,13 +97,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1779,24 +1800,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="15.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>10</v>
       </c>
@@ -1807,7 +1832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>50</v>
       </c>
@@ -1818,7 +1843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>100</v>
       </c>
@@ -1829,7 +1854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>250</v>
       </c>
@@ -1840,7 +1865,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f>A5+250</f>
         <v>500</v>
@@ -1852,7 +1877,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f t="shared" ref="A7:A10" si="0">A6+250</f>
         <v>750</v>
@@ -1864,7 +1889,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>1000</v>
@@ -1876,7 +1901,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>1250</v>
@@ -1888,7 +1913,7 @@
         <v>1976</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>1500</v>
@@ -1900,7 +1925,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f>A10+250</f>
         <v>1750</v>
@@ -1912,7 +1937,7 @@
         <v>3681</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f t="shared" ref="A12" si="1">A11+250</f>
         <v>2000</v>
@@ -1922,6 +1947,89 @@
       </c>
       <c r="C12" s="1">
         <v>5402</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>100</v>
+      </c>
+      <c r="B16">
+        <f>0.002635*1000</f>
+        <v>2.6350000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>200</v>
+      </c>
+      <c r="B17">
+        <f>0.019809*1000</f>
+        <v>19.809000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>300</v>
+      </c>
+      <c r="B18">
+        <f>0.0472262*1000</f>
+        <v>47.226200000000006</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>400</v>
+      </c>
+      <c r="B19">
+        <f>0.159812*1000</f>
+        <v>159.81200000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>500</v>
+      </c>
+      <c r="B20">
+        <f>0.265982*1000</f>
+        <v>265.98199999999997</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>1000</v>
+      </c>
+      <c r="B21">
+        <f>2.19936*1000</f>
+        <v>2199.36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>1500</v>
+      </c>
+      <c r="B22">
+        <f>8.02158*1000</f>
+        <v>8021.58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>2000</v>
+      </c>
+      <c r="B23">
+        <f>18.6438*1000</f>
+        <v>18643.8</v>
       </c>
     </row>
   </sheetData>
